--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104608_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104608_W17.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7901</v>
+        <v>4.8376</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1489</v>
+        <v>2.9789</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6413</v>
+        <v>1.8586</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4675</v>
+        <v>5.4296</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005</v>
+        <v>-0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>5.467</v>
+        <v>5.4622</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7283</v>
+        <v>4.6656</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3441</v>
+        <v>-0.3909</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0724</v>
+        <v>5.0565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7392</v>
+        <v>0.7639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0919</v>
+        <v>0.1835</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3902</v>
+        <v>0.2968</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2982</v>
+        <v>-0.1133</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9961</v>
+        <v>-1.0032</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.8354</v>
+        <v>-0.8454</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7815</v>
+        <v>3.2364</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9788</v>
+        <v>2.3294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8027</v>
+        <v>0.9069</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6048</v>
+        <v>1.5977</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4389</v>
+        <v>2.4307</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6843</v>
+        <v>1.6699</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1243</v>
+        <v>2.1148</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2694</v>
+        <v>0.7281</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2945</v>
+        <v>0.6595</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0251</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1141</v>
+        <v>0.2332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8616</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.5596</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1551</v>
+        <v>0.0347</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2683</v>
+        <v>-0.8101</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4233</v>
+        <v>0.8448</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5228</v>
+        <v>0.2356</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7895</v>
+        <v>0.1239</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2666</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6779</v>
+        <v>-0.2009</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1567</v>
+        <v>0.7331</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2296</v>
+        <v>0.3774</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3388</v>
+        <v>0.5571</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1092</v>
+        <v>-0.1797</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1344</v>
+        <v>0.1358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3523</v>
+        <v>1.1249</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4867</v>
+        <v>-0.9891</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0258</v>
+        <v>-1.141</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8139</v>
+        <v>0.2753</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8397</v>
+        <v>-1.4163</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2434</v>
+        <v>0.5029</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1314</v>
+        <v>0.7789</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>-0.276</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2176</v>
+        <v>-1.6439</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9453</v>
+        <v>-0.5036</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7277</v>
+        <v>-1.1403</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0251</v>
+        <v>0.2265</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1089</v>
+        <v>0.622</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0838</v>
+        <v>-0.3954</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6629</v>
+        <v>-0.3851</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3686</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0315</v>
+        <v>-1.3303</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6744</v>
+        <v>-1.535</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7997</v>
+        <v>-0.8814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1253</v>
+        <v>-0.6536</v>
       </c>
       <c r="J6" t="n">
-        <v>0.169</v>
+        <v>-0.0327</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3983</v>
+        <v>-0.6657</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2293</v>
+        <v>0.633</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8434</v>
+        <v>-1.5023</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.198</v>
+        <v>-0.2157</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>-1.2866</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5598</v>
+        <v>-0.8501</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3338</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.774</v>
+        <v>-0.7385</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8143</v>
+        <v>-0.6217</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6548</v>
+        <v>0.0968</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4691</v>
+        <v>-0.7184</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5368</v>
+        <v>-0.6602</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8758</v>
+        <v>-0.7822</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.661</v>
+        <v>0.122</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0205</v>
+        <v>0.1577</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6549</v>
+        <v>0.3964</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6344</v>
+        <v>-0.2388</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5162</v>
+        <v>-0.8179</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2209</v>
+        <v>-1.1786</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2954</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2775</v>
+        <v>0.5816</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>1.0772</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8602</v>
+        <v>-0.4956</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3581</v>
+        <v>-1.6092</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3132</v>
+        <v>-0.5997</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.045</v>
+        <v>-1.0096</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3457</v>
+        <v>-1.3432</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2871</v>
+        <v>-1.2867</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.594</v>
+        <v>-0.5881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0124</v>
+        <v>-0.266</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4386</v>
+        <v>0.1555</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4509</v>
+        <v>-0.4215</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5951</v>
+        <v>-1.8748</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4456</v>
+        <v>0.5042</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0408</v>
+        <v>-2.379</v>
       </c>
       <c r="G9" t="n">
-        <v>0.19</v>
+        <v>0.1923</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2988</v>
+        <v>1.2928</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1088</v>
+        <v>-1.1005</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3238</v>
+        <v>2.2956</v>
       </c>
       <c r="K9" t="n">
-        <v>1.804</v>
+        <v>1.7819</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1338</v>
+        <v>-2.1032</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3756</v>
+        <v>0.0907</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3902</v>
+        <v>0.485</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0145</v>
+        <v>-0.3943</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9741</v>
+        <v>-2.8433</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0014</v>
+        <v>-1.9649</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9727</v>
+        <v>-0.8784</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1433</v>
+        <v>-3.1636</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.245</v>
+        <v>-2.2623</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8983</v>
+        <v>-0.9014</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3717</v>
+        <v>-2.4195</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3933</v>
+        <v>-1.4284</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9784</v>
+        <v>-0.9912</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7716</v>
+        <v>-0.7441</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.672</v>
+        <v>-0.5203</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2511</v>
+        <v>0.3456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9231</v>
+        <v>-0.8659</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4545</v>
+        <v>-3.1509</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6552</v>
+        <v>-1.4611</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7992</v>
+        <v>-1.6899</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.016</v>
+        <v>-3.6295</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4833</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5327</v>
+        <v>-4.25</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0242</v>
+        <v>-1.9115</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4515</v>
+        <v>1.2098</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5727</v>
+        <v>-3.1213</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008200000000000001</v>
+        <v>-1.718</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0318</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04</v>
+        <v>-1.1287</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2005</v>
+        <v>0.6167</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>0.4991</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1685</v>
+        <v>0.1176</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9575</v>
+        <v>-3.3321</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4656</v>
+        <v>-2.764</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4919</v>
+        <v>-0.5681</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6228</v>
+        <v>-3.0219</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6234</v>
+        <v>-1.4875</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.2462</v>
+        <v>-1.5344</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8857</v>
+        <v>-3.0379</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2224</v>
+        <v>-1.4586</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.1081</v>
+        <v>-1.5793</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7371</v>
+        <v>0.016</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.599</v>
+        <v>-0.0289</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1381</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2005</v>
+        <v>0.324</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5383</v>
+        <v>0.2739</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3378</v>
+        <v>0.0501</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3888</v>
+        <v>-5.1995</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8137</v>
+        <v>-2.6198</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5751</v>
+        <v>-2.5797</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.0962</v>
+        <v>-5.0974</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6363</v>
+        <v>-1.637</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4599</v>
+        <v>-3.4604</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1628</v>
+        <v>-2.1873</v>
       </c>
       <c r="K13" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9334</v>
+        <v>-2.9102</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4514</v>
+        <v>-0.2614</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6775</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.774</v>
+        <v>-0.8093</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.654</v>
+        <v>-10.5736</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.438500000000001</v>
+        <v>-0.6374000000000004</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.2155</v>
+        <v>-9.9366</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.3022</v>
+        <v>-12.3375</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.7841</v>
+        <v>-7.824199999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.517900000000001</v>
+        <v>-4.513399999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5450000000000021</v>
+        <v>-0.8168000000000006</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5309000000000001</v>
+        <v>-0.7083999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0141</v>
+        <v>-0.1087000000000007</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.7571</v>
+        <v>-11.5209</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.2532</v>
+        <v>-7.1158</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.504</v>
+        <v>-4.4047</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.939299999999999</v>
+        <v>-7.967300000000002</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8619000000000002</v>
+        <v>1.2307</v>
       </c>
       <c r="T14" t="n">
-        <v>3.281899999999999</v>
+        <v>5.408</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.143699999999999</v>
+        <v>-4.1772</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.8924</v>
+        <v>-2.881400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7641</v>
+        <v>2.7386</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.6564</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.468</v>
+        <v>5.7963</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5558</v>
+        <v>4.2528</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9122</v>
+        <v>1.5436</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1715</v>
+        <v>6.0227</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3421</v>
+        <v>-0.1034</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1706</v>
+        <v>6.1261</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4455</v>
+        <v>5.5759</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2535</v>
+        <v>0.3857</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.192</v>
+        <v>5.1902</v>
       </c>
       <c r="M15" t="n">
-        <v>0.617</v>
+        <v>0.4468</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5956</v>
+        <v>-0.4891</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0214</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>3.629</v>
+        <v>-0.3159</v>
       </c>
       <c r="T15" t="n">
-        <v>2.468</v>
+        <v>-0.2744</v>
       </c>
       <c r="U15" t="n">
-        <v>1.161</v>
+        <v>-0.0414</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1212</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1212</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.0612</v>
+        <v>3.7367</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8291</v>
+        <v>4.3432</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2321</v>
+        <v>-0.6065</v>
       </c>
       <c r="G16" t="n">
-        <v>6.0374</v>
+        <v>4.4896</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1039</v>
+        <v>2.7421</v>
       </c>
       <c r="I16" t="n">
-        <v>6.1413</v>
+        <v>1.7475</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6176</v>
+        <v>4.1558</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4014</v>
+        <v>1.8099</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2162</v>
+        <v>2.3459</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4197</v>
+        <v>0.3338</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5053</v>
+        <v>0.9322</v>
       </c>
       <c r="O16" t="n">
-        <v>0.925</v>
+        <v>-0.5984</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0688</v>
+        <v>0.525</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.747</v>
+        <v>1.2863</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3218</v>
+        <v>-0.7614</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>1.405</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6995</v>
+        <v>3.4848</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8393</v>
+        <v>1.4466</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1398</v>
+        <v>2.0382</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4717</v>
+        <v>0.1681</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7284</v>
+        <v>0.3363</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7433</v>
+        <v>-0.1682</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1692</v>
+        <v>-0.4815</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8183</v>
+        <v>-0.28</v>
       </c>
       <c r="L17" t="n">
-        <v>2.351</v>
+        <v>-0.2015</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3025</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9102</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6077</v>
+        <v>0.0333</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4942</v>
+        <v>1.6645</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7512</v>
+        <v>1.414</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.257</v>
+        <v>0.2504</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3214</v>
+        <v>2.1075</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4141</v>
+        <v>2.1075</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7479</v>
+        <v>1.9306</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8634</v>
+        <v>1.5745</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8844</v>
+        <v>0.3561</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.481</v>
+        <v>3.2854</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8065</v>
+        <v>2.7551</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2875</v>
+        <v>0.5303</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1174</v>
+        <v>2.5503</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1704</v>
+        <v>2.2678</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.053</v>
+        <v>0.2826</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5984</v>
+        <v>0.7351</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3639</v>
+        <v>0.4873</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2345</v>
+        <v>0.2477</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8167</v>
+        <v>-0.0392</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2411</v>
+        <v>0.1623</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5755</v>
+        <v>-0.2016</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7496</v>
+        <v>1.6897</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1466</v>
+        <v>1.6954</v>
       </c>
       <c r="F19" t="n">
-        <v>0.603</v>
+        <v>-0.0057</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2997</v>
+        <v>2.3814</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7693</v>
+        <v>0.8008</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5304</v>
+        <v>1.5806</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5923</v>
+        <v>1.5911</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2991</v>
+        <v>1.003</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2931</v>
+        <v>0.5881</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7074</v>
+        <v>0.7903</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4701</v>
+        <v>-0.2022</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2373</v>
+        <v>0.9925</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2287</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3115</v>
+        <v>0.1043</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0828</v>
+        <v>-0.8659</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0262</v>
+        <v>1.1619</v>
       </c>
       <c r="E20" t="n">
-        <v>1.122</v>
+        <v>0.6565</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0959</v>
+        <v>0.5054</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3701</v>
+        <v>-0.4792</v>
       </c>
       <c r="H20" t="n">
-        <v>0.792</v>
+        <v>0.8125</v>
       </c>
       <c r="I20" t="n">
-        <v>1.578</v>
+        <v>-1.2917</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6089</v>
+        <v>0.0925</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0146</v>
+        <v>1.1581</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5944</v>
+        <v>-1.0656</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7611</v>
+        <v>-0.5717</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2225</v>
+        <v>-0.3457</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9837</v>
+        <v>-0.226</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.41</v>
+        <v>1.2345</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>1.068</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9231</v>
+        <v>0.1666</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4529</v>
+        <v>0.5271</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3446</v>
+        <v>1.0492</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7974</v>
+        <v>-0.5221</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6604</v>
+        <v>0.6755</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1127</v>
+        <v>-0.1039</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7731</v>
+        <v>0.7793</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1097</v>
+        <v>1.1053</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4494</v>
+        <v>-0.4298</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2455</v>
+        <v>-0.2881</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.0561</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4803</v>
+        <v>-0.232</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9215</v>
+        <v>-0.5939</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1041</v>
+        <v>-0.7301</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8174</v>
+        <v>0.1362</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4703</v>
+        <v>-1.1969</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6304999999999999</v>
+        <v>-1.4307</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1008</v>
+        <v>0.2337</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3854</v>
+        <v>-0.1791</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4227</v>
+        <v>-0.4244</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.2453</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0849</v>
+        <v>-1.0179</v>
       </c>
       <c r="N22" t="n">
-        <v>1.0532</v>
+        <v>-1.0062</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1381</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5054</v>
+        <v>-0.5563</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0525</v>
+        <v>-0.2535</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5471</v>
+        <v>-0.3028</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8639</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3258</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0575</v>
+        <v>-0.5795</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2682</v>
+        <v>-0.3555</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2001</v>
+        <v>-0.457</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4373</v>
+        <v>0.6345</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2372</v>
+        <v>-1.0915</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1567</v>
+        <v>-0.3904</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4125</v>
+        <v>-0.4277</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2558</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0434</v>
+        <v>-0.0665</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0248</v>
+        <v>1.0622</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0186</v>
+        <v>-1.1287</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2845</v>
+        <v>0.4749</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>0.5849</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6766</v>
+        <v>-0.11</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.8634</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7712</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0638</v>
+        <v>-1.3383</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3701</v>
+        <v>-1.3937</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3063</v>
+        <v>0.0553</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0055</v>
+        <v>-2.5604</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1891</v>
+        <v>1.5676</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1946</v>
+        <v>-4.128</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0373</v>
+        <v>-2.5363</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0373</v>
+        <v>-3.3152</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0318</v>
+        <v>-0.0241</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1891</v>
+        <v>0.7887</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1573</v>
+        <v>-0.8129</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0278</v>
+        <v>-0.3227</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1391</v>
+        <v>0.2808</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1113</v>
+        <v>-0.6034</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3344</v>
+        <v>-1.887</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9536</v>
+        <v>-2.26</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3808</v>
+        <v>0.373</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.5627</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5582</v>
+        <v>-0.1868</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.121</v>
+        <v>0.1952</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5079</v>
+        <v>0.0372</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7895</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.2974</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0548</v>
+        <v>-0.0289</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7688</v>
+        <v>-0.1868</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8236</v>
+        <v>0.1579</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3181</v>
+        <v>0.1533</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3115</v>
+        <v>-0.021</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0066</v>
+        <v>0.1743</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.65399999999999</v>
+        <v>13.5729</v>
       </c>
       <c r="E26" t="n">
-        <v>10.2155</v>
+        <v>10.0549</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4385</v>
+        <v>3.518</v>
       </c>
       <c r="G26" t="n">
-        <v>12.3022</v>
+        <v>12.3376</v>
       </c>
       <c r="H26" t="n">
-        <v>7.784000000000002</v>
+        <v>7.8241</v>
       </c>
       <c r="I26" t="n">
-        <v>4.517999999999999</v>
+        <v>4.513299999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>11.7569</v>
+        <v>11.5208</v>
       </c>
       <c r="K26" t="n">
-        <v>7.253100000000001</v>
+        <v>7.1159</v>
       </c>
       <c r="L26" t="n">
-        <v>4.5039</v>
+        <v>4.4049</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.8168000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5311000000000001</v>
+        <v>0.7082999999999998</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01400000000000023</v>
+        <v>0.1085000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.4026</v>
+        <v>-3.4146</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R26" t="n">
-        <v>7.939100000000001</v>
+        <v>7.9671</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8619000000000001</v>
+        <v>1.7684</v>
       </c>
       <c r="T26" t="n">
-        <v>4.143700000000001</v>
+        <v>4.2956</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2819</v>
+        <v>-2.5272</v>
       </c>
       <c r="V26" t="n">
-        <v>2.8925</v>
+        <v>2.881399999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6565</v>
+        <v>5.6201</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.7641</v>
+        <v>-2.7387</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104608_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104608_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.62</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104608_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-2.7387</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
